--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,9 +262,6 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cet attribut peut contenir le code représentant : • un évènement documenté (acte, traitement, diagnostic, etc…),  • une modalité d'acquisition, • une région anatomique. </t>
   </si>
   <si>
     <t>Cet attribut peut contenir le code représentant : • un évènement documenté (acte, traitement, diagnostic, etc…),  • une modalité d'acquisition, • une région anatomique.</t>
@@ -853,7 +850,7 @@
         <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>

--- a/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-event-code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
